--- a/Sindhi Muslim/Weekly Diary/Weekly Diary - 14-01-2025.xlsx
+++ b/Sindhi Muslim/Weekly Diary/Weekly Diary - 14-01-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Weekly Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BF6FB6-0E09-4302-ADFE-539779CA120B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061257CF-212C-47C9-B8A2-38E247BD7F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC0A426B-C469-4DBE-A695-5879DF716B89}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="32">
   <si>
     <t>Date</t>
   </si>
@@ -67,15 +67,6 @@
     <t>Weekly Diary - ECE (ROSE)</t>
   </si>
   <si>
-    <t>Learn Counting (1-20)</t>
-  </si>
-  <si>
-    <t>Learn Poem, Page No# 105</t>
-  </si>
-  <si>
-    <t>Learn Page No# 99</t>
-  </si>
-  <si>
     <t>Do Home Work Page No# 112, 113 &amp; 114</t>
   </si>
   <si>
@@ -109,28 +100,37 @@
     <t>Oral Counting (1-50)</t>
   </si>
   <si>
-    <t>Do H.W Page No# 98, 99 &amp; 100</t>
-  </si>
-  <si>
-    <t>Do H.W Page No# 111, 112 &amp; 113</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Do H.W Page No# 98</t>
-  </si>
-  <si>
-    <t>Do H.W Page No# 102, 103 &amp; 104</t>
-  </si>
-  <si>
-    <t>Do H.W Page No# 115, 116 &amp; 117</t>
-  </si>
-  <si>
-    <t>حروف تہجی ا سے ش تک</t>
-  </si>
-  <si>
-    <t>Learn Table No# 2</t>
+    <t>Do H.W Page No# 105 &amp; 106</t>
+  </si>
+  <si>
+    <t>Do H.W Page No# 110 &amp; 112</t>
+  </si>
+  <si>
+    <t>Kashmir Day</t>
+  </si>
+  <si>
+    <t>Do H.W Page No# 126, 127 &amp; 128</t>
+  </si>
+  <si>
+    <t>Do H.W Page No# 108, 109 &amp; 110</t>
+  </si>
+  <si>
+    <t>Do H.W Page No# 113, 114 &amp; 116</t>
+  </si>
+  <si>
+    <t>حروف تہجی (ا سے ظ تک)</t>
+  </si>
+  <si>
+    <t>Learn Table of 2</t>
+  </si>
+  <si>
+    <t>Learn Page No# 105</t>
+  </si>
+  <si>
+    <t>Learn Page No# 107</t>
+  </si>
+  <si>
+    <t>Learn Counting (1 - 20)</t>
   </si>
 </sst>
 </file>
@@ -184,15 +184,21 @@
       <family val="5"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -531,11 +537,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -666,6 +709,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1029,110 +1087,106 @@
     </row>
     <row r="4" spans="1:5" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
-        <v>45670</v>
+        <v>45691</v>
       </c>
       <c r="B4" s="13" t="str">
         <f>TEXT(A4,"dddd")</f>
         <v>Monday</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
-        <v>45671</v>
+        <v>45692</v>
       </c>
       <c r="B5" s="13" t="str">
         <f t="shared" ref="B5:B8" si="0">TEXT(A5,"dddd")</f>
         <v>Tuesday</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
-        <v>45672</v>
-      </c>
-      <c r="B6" s="13" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="8" customFormat="1" ht="26.25" x14ac:dyDescent="0.35">
+      <c r="A6" s="45">
+        <v>45693</v>
+      </c>
+      <c r="B6" s="46" t="str">
         <f t="shared" si="0"/>
         <v>Wednesday</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>30</v>
-      </c>
+      <c r="C6" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
-        <v>45673</v>
+        <v>45694</v>
       </c>
       <c r="B7" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Thursday</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
-        <v>45674</v>
+        <v>45695</v>
       </c>
       <c r="B8" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Friday</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="18">
-        <v>45675</v>
+        <v>45696</v>
       </c>
       <c r="B9" s="10" t="str">
         <f t="shared" ref="B9" si="1">TEXT(A9,"dddd")</f>
         <v>Saturday</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1171,110 +1225,106 @@
     </row>
     <row r="14" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
-        <v>45670</v>
+        <v>45691</v>
       </c>
       <c r="B14" s="13" t="str">
         <f>TEXT(A14,"dddd")</f>
         <v>Monday</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
-        <v>45671</v>
+        <v>45692</v>
       </c>
       <c r="B15" s="13" t="str">
         <f t="shared" ref="B15:B19" si="2">TEXT(A15,"dddd")</f>
         <v>Tuesday</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>45672</v>
-      </c>
-      <c r="B16" s="13" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="45">
+        <v>45693</v>
+      </c>
+      <c r="B16" s="46" t="str">
         <f t="shared" si="2"/>
         <v>Wednesday</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>30</v>
-      </c>
+      <c r="C16" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="48"/>
+      <c r="E16" s="49"/>
     </row>
     <row r="17" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
-        <v>45673</v>
+        <v>45694</v>
       </c>
       <c r="B17" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thursday</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
-        <v>45674</v>
+        <v>45695</v>
       </c>
       <c r="B18" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Friday</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
-        <v>45675</v>
+        <v>45696</v>
       </c>
       <c r="B19" s="10" t="str">
         <f t="shared" si="2"/>
         <v>Saturday</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1313,110 +1363,106 @@
     </row>
     <row r="24" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
-        <v>45670</v>
+        <v>45691</v>
       </c>
       <c r="B24" s="13" t="str">
         <f>TEXT(A24,"dddd")</f>
         <v>Monday</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
-        <v>45671</v>
+        <v>45692</v>
       </c>
       <c r="B25" s="13" t="str">
         <f t="shared" ref="B25:B29" si="3">TEXT(A25,"dddd")</f>
         <v>Tuesday</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
-        <v>45672</v>
-      </c>
-      <c r="B26" s="13" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="45">
+        <v>45693</v>
+      </c>
+      <c r="B26" s="46" t="str">
         <f t="shared" si="3"/>
         <v>Wednesday</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>30</v>
-      </c>
+      <c r="C26" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="48"/>
+      <c r="E26" s="49"/>
     </row>
     <row r="27" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
-        <v>45673</v>
+        <v>45694</v>
       </c>
       <c r="B27" s="13" t="str">
         <f t="shared" si="3"/>
         <v>Thursday</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
-        <v>45674</v>
+        <v>45695</v>
       </c>
       <c r="B28" s="13" t="str">
         <f t="shared" si="3"/>
         <v>Friday</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18">
-        <v>45675</v>
+        <v>45696</v>
       </c>
       <c r="B29" s="10" t="str">
         <f t="shared" si="3"/>
         <v>Saturday</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1455,110 +1501,106 @@
     </row>
     <row r="34" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
-        <v>45670</v>
+        <v>45691</v>
       </c>
       <c r="B34" s="13" t="str">
         <f>TEXT(A34,"dddd")</f>
         <v>Monday</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
-        <v>45671</v>
+        <v>45692</v>
       </c>
       <c r="B35" s="13" t="str">
         <f t="shared" ref="B35:B39" si="4">TEXT(A35,"dddd")</f>
         <v>Tuesday</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="12">
-        <v>45672</v>
-      </c>
-      <c r="B36" s="13" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="45">
+        <v>45693</v>
+      </c>
+      <c r="B36" s="46" t="str">
         <f t="shared" si="4"/>
         <v>Wednesday</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>30</v>
-      </c>
+      <c r="C36" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="48"/>
+      <c r="E36" s="49"/>
     </row>
     <row r="37" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
-        <v>45673</v>
+        <v>45694</v>
       </c>
       <c r="B37" s="13" t="str">
         <f t="shared" si="4"/>
         <v>Thursday</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
-        <v>45674</v>
+        <v>45695</v>
       </c>
       <c r="B38" s="13" t="str">
         <f t="shared" si="4"/>
         <v>Friday</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="18">
-        <v>45675</v>
+        <v>45696</v>
       </c>
       <c r="B39" s="10" t="str">
         <f t="shared" si="4"/>
         <v>Saturday</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1597,119 +1639,120 @@
     </row>
     <row r="44" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
-        <v>45670</v>
+        <v>45691</v>
       </c>
       <c r="B44" s="13" t="str">
         <f>TEXT(A44,"dddd")</f>
         <v>Monday</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
-        <v>45671</v>
+        <v>45692</v>
       </c>
       <c r="B45" s="13" t="str">
         <f t="shared" ref="B45:B49" si="5">TEXT(A45,"dddd")</f>
         <v>Tuesday</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
-        <v>45672</v>
-      </c>
-      <c r="B46" s="13" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A46" s="45">
+        <v>45693</v>
+      </c>
+      <c r="B46" s="46" t="str">
         <f t="shared" si="5"/>
         <v>Wednesday</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>30</v>
-      </c>
+      <c r="C46" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="48"/>
+      <c r="E46" s="49"/>
     </row>
     <row r="47" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
-        <v>45673</v>
+        <v>45694</v>
       </c>
       <c r="B47" s="13" t="str">
         <f t="shared" si="5"/>
         <v>Thursday</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
-        <v>45674</v>
+        <v>45695</v>
       </c>
       <c r="B48" s="13" t="str">
         <f t="shared" si="5"/>
         <v>Friday</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="18">
-        <v>45675</v>
+        <v>45696</v>
       </c>
       <c r="B49" s="10" t="str">
         <f t="shared" si="5"/>
         <v>Saturday</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
+    <mergeCell ref="C46:E46"/>
     <mergeCell ref="A41:E42"/>
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="A11:E12"/>
     <mergeCell ref="A21:E22"/>
     <mergeCell ref="A31:E32"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C36:E36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -1778,10 +1821,10 @@
         <v>4</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
@@ -1796,10 +1839,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
@@ -1814,10 +1857,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
@@ -1832,7 +1875,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E7" s="9"/>
     </row>
@@ -1848,10 +1891,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
@@ -1861,10 +1904,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1913,10 +1956,10 @@
         <v>4</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -1931,10 +1974,10 @@
         <v>5</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -1949,10 +1992,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -1967,7 +2010,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E17" s="9"/>
     </row>
@@ -1983,10 +2026,10 @@
         <v>3</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
@@ -1996,10 +2039,10 @@
         <v>5</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2048,10 +2091,10 @@
         <v>4</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2066,10 +2109,10 @@
         <v>5</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2084,10 +2127,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2102,7 +2145,7 @@
         <v>4</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E27" s="9"/>
     </row>
@@ -2118,10 +2161,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
@@ -2131,10 +2174,10 @@
         <v>5</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2183,10 +2226,10 @@
         <v>4</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2201,10 +2244,10 @@
         <v>5</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2219,10 +2262,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2237,7 +2280,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E37" s="9"/>
     </row>
@@ -2253,10 +2296,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
@@ -2266,10 +2309,10 @@
         <v>5</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2318,10 +2361,10 @@
         <v>4</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2336,10 +2379,10 @@
         <v>5</v>
       </c>
       <c r="D45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2354,10 +2397,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -2372,7 +2415,7 @@
         <v>4</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E47" s="9"/>
     </row>
@@ -2388,10 +2431,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
@@ -2401,21 +2444,14 @@
         <v>5</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A21:E22"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="A11:E12"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
     <mergeCell ref="A41:E42"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="B48:B49"/>
@@ -2424,6 +2460,13 @@
     <mergeCell ref="A31:E32"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A21:E22"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A11:E12"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
